--- a/shemas-plantUML/ig/cm-v3-administrative-gender.xlsx
+++ b/shemas-plantUML/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T13:51:35+00:00</t>
+    <t>2026-06-16T14:08:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/shemas-plantUML/ig/cm-v3-administrative-gender.xlsx
+++ b/shemas-plantUML/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T14:08:54+00:00</t>
+    <t>2026-06-16T14:27:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/shemas-plantUML/ig/cm-v3-administrative-gender.xlsx
+++ b/shemas-plantUML/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T14:27:50+00:00</t>
+    <t>2026-06-16T14:39:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
